--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -660,31 +660,31 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>0.5025559999999998</v>
+        <v>0.5035359999999998</v>
       </c>
       <c r="D2">
-        <v>0.4879279999999993</v>
+        <v>0.4889879999999993</v>
       </c>
       <c r="E2">
-        <v>0.4850537176443364</v>
+        <v>0.4880998606769701</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="H2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="I2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -699,13 +699,13 @@
         <v>68</v>
       </c>
       <c r="P2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="S2" t="s">
         <v>69</v>
@@ -725,31 +725,31 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>0.4686639999999987</v>
+        <v>0.4674799999999988</v>
       </c>
       <c r="D3">
-        <v>0.4831359999999993</v>
+        <v>0.4820999999999993</v>
       </c>
       <c r="E3">
-        <v>0.4848653204771308</v>
+        <v>0.4816348617949026</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="H3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="I3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -764,13 +764,13 @@
         <v>68</v>
       </c>
       <c r="P3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="S3" t="s">
         <v>69</v>
@@ -790,25 +790,25 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>1.128</v>
+        <v>1.076</v>
       </c>
       <c r="D4">
-        <v>1.252</v>
+        <v>1.236</v>
       </c>
       <c r="E4">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="F4">
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="L4">
         <v>0.8200692764238203</v>
@@ -823,10 +823,10 @@
         <v>68</v>
       </c>
       <c r="P4">
-        <v>1.036948324347409</v>
+        <v>0.9850884312991284</v>
       </c>
       <c r="Q4">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -835,10 +835,10 @@
         <v>70</v>
       </c>
       <c r="T4">
-        <v>0.01087699950497645</v>
+        <v>0.01854031901818742</v>
       </c>
       <c r="U4">
-        <v>-0.03694832434740891</v>
+        <v>0.01491156870087162</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -849,25 +849,25 @@
         <v>64</v>
       </c>
       <c r="C5">
-        <v>1.412</v>
+        <v>1.344</v>
       </c>
       <c r="D5">
-        <v>1.808</v>
+        <v>1.788</v>
       </c>
       <c r="E5">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F5">
         <v>2.2</v>
       </c>
       <c r="G5">
-        <v>1.603126377165344</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L5">
         <v>1.746417103282563</v>
@@ -882,10 +882,10 @@
         <v>68</v>
       </c>
       <c r="P5">
-        <v>1.717926703142854</v>
+        <v>1.501280428022223</v>
       </c>
       <c r="Q5">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R5">
         <v>2</v>
@@ -894,10 +894,10 @@
         <v>70</v>
       </c>
       <c r="T5">
-        <v>0.01802007627663649</v>
+        <v>0.02825555268635682</v>
       </c>
       <c r="U5">
-        <v>0.2820732968571464</v>
+        <v>0.4987195719777766</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -908,25 +908,25 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>7.968</v>
+        <v>7.772</v>
       </c>
       <c r="D6">
-        <v>8.868</v>
+        <v>8.804</v>
       </c>
       <c r="E6">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="F6">
         <v>9.4</v>
       </c>
       <c r="G6">
-        <v>8.402378129921239</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="L6">
         <v>4.467028425282805</v>
@@ -941,10 +941,10 @@
         <v>68</v>
       </c>
       <c r="P6">
-        <v>10.16489315578537</v>
+        <v>9.957671677471454</v>
       </c>
       <c r="Q6">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -953,10 +953,10 @@
         <v>70</v>
       </c>
       <c r="T6">
-        <v>0.1066239611247735</v>
+        <v>0.1874130318789931</v>
       </c>
       <c r="U6">
-        <v>-0.1648931557853732</v>
+        <v>0.04232832252854557</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -967,25 +967,25 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="D7">
-        <v>4.812</v>
+        <v>4.696</v>
       </c>
       <c r="E7">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>4.153921090288683</v>
+        <v>4.046198812423416</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="L7">
         <v>2.262338789582505</v>
@@ -1000,22 +1000,22 @@
         <v>68</v>
       </c>
       <c r="P7">
-        <v>5.645415907992541</v>
+        <v>5.269620245019544</v>
       </c>
       <c r="Q7">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S7" t="s">
         <v>70</v>
       </c>
       <c r="T7">
-        <v>0.05921720937758934</v>
+        <v>0.09917936029206498</v>
       </c>
       <c r="U7">
-        <v>0.3545840920074594</v>
+        <v>-0.269620245019544</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1026,25 +1026,25 @@
         <v>64</v>
       </c>
       <c r="C8">
-        <v>13.58</v>
+        <v>13.548</v>
       </c>
       <c r="D8">
-        <v>14.788</v>
+        <v>14.728</v>
       </c>
       <c r="E8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -1059,10 +1059,10 @@
         <v>68</v>
       </c>
       <c r="P8">
-        <v>19.21302027199633</v>
+        <v>19.20064674567716</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R8">
         <v>19</v>
@@ -1071,10 +1071,10 @@
         <v>70</v>
       </c>
       <c r="T8">
-        <v>0.2015336802044807</v>
+        <v>0.3613747808924153</v>
       </c>
       <c r="U8">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1085,25 +1085,25 @@
         <v>64</v>
       </c>
       <c r="C9">
-        <v>3.184</v>
+        <v>2.824</v>
       </c>
       <c r="D9">
-        <v>4.004</v>
+        <v>3.956</v>
       </c>
       <c r="E9">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="F9">
         <v>5.8</v>
       </c>
       <c r="G9">
-        <v>3.579766740594905</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="L9">
         <v>7.059923274159115</v>
@@ -1118,22 +1118,22 @@
         <v>68</v>
       </c>
       <c r="P9">
-        <v>1.566812662552681</v>
+        <v>0.8599057302044893</v>
       </c>
       <c r="Q9">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>70</v>
       </c>
       <c r="T9">
-        <v>0.01643497574066832</v>
+        <v>0.01618425925734723</v>
       </c>
       <c r="U9">
-        <v>0.433187337447319</v>
+        <v>0.1400942697955107</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1144,25 +1144,25 @@
         <v>64</v>
       </c>
       <c r="C10">
-        <v>172.984</v>
+        <v>173.496</v>
       </c>
       <c r="D10">
-        <v>170.488</v>
+        <v>170.784</v>
       </c>
       <c r="E10">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F10">
         <v>169.2</v>
       </c>
       <c r="G10">
-        <v>171.7793246530184</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L10">
         <v>4.764861070548267</v>
@@ -1177,22 +1177,22 @@
         <v>68</v>
       </c>
       <c r="P10">
-        <v>174.4769462223457</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q10">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R10">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S10" t="s">
         <v>70</v>
       </c>
       <c r="T10">
-        <v>1.830164158743969</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U10">
-        <v>-0.4769462223457026</v>
+        <v>0.01929604709013688</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1203,25 +1203,25 @@
         <v>64</v>
       </c>
       <c r="C11">
-        <v>3.948</v>
+        <v>3.444</v>
       </c>
       <c r="D11">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="E11">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="F11">
         <v>7.4</v>
       </c>
       <c r="G11">
-        <v>4.417128380314937</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="L11">
         <v>9.933150479214353</v>
@@ -1236,22 +1236,22 @@
         <v>68</v>
       </c>
       <c r="P11">
-        <v>1.178036751837105</v>
+        <v>0.2450827893961431</v>
       </c>
       <c r="Q11">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="s">
         <v>70</v>
       </c>
       <c r="T11">
-        <v>0.01235693704856522</v>
+        <v>0.004612695629040375</v>
       </c>
       <c r="U11">
-        <v>-0.1780367518371049</v>
+        <v>-0.2450827893961431</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1262,25 +1262,25 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>3.692</v>
+        <v>3.784</v>
       </c>
       <c r="D12">
-        <v>3.192</v>
+        <v>3.252</v>
       </c>
       <c r="E12">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.450678816710424</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L12">
         <v>0.887818750560327</v>
@@ -1295,22 +1295,22 @@
         <v>68</v>
       </c>
       <c r="P12">
-        <v>3.440193613933819</v>
+        <v>3.590592119879259</v>
       </c>
       <c r="Q12">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12" t="s">
         <v>70</v>
       </c>
       <c r="T12">
-        <v>-0.03526554980344976</v>
+        <v>-0.06604255040874341</v>
       </c>
       <c r="U12">
-        <v>-0.4401936139338187</v>
+        <v>0.409407880120741</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1321,25 +1321,25 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>1.832</v>
+        <v>1.904</v>
       </c>
       <c r="D13">
-        <v>1.772</v>
+        <v>1.796</v>
       </c>
       <c r="E13">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F13">
         <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L13">
         <v>1.198624596172324</v>
@@ -1354,22 +1354,22 @@
         <v>68</v>
       </c>
       <c r="P13">
-        <v>2.528722469358031</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q13">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="s">
         <v>70</v>
       </c>
       <c r="T13">
-        <v>-0.02592202596419435</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U13">
-        <v>-0.5287224693580312</v>
+        <v>0.4427846049148738</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1380,25 +1380,25 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>13.316</v>
+        <v>13.532</v>
       </c>
       <c r="D14">
-        <v>12.472</v>
+        <v>12.556</v>
       </c>
       <c r="E14">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F14">
         <v>11.8</v>
       </c>
       <c r="G14">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L14">
         <v>3.125306797245826</v>
@@ -1413,10 +1413,10 @@
         <v>68</v>
       </c>
       <c r="P14">
-        <v>12.85213593315269</v>
+        <v>13.11473458118962</v>
       </c>
       <c r="Q14">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R14">
         <v>13</v>
@@ -1425,10 +1425,10 @@
         <v>70</v>
       </c>
       <c r="T14">
-        <v>-0.1317477126855753</v>
+        <v>-0.2412221969964765</v>
       </c>
       <c r="U14">
-        <v>0.1478640668473066</v>
+        <v>-0.1147345811896248</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1439,25 +1439,25 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>8.612</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D15">
-        <v>6.564</v>
+        <v>6.752</v>
       </c>
       <c r="E15">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F15">
         <v>6.6</v>
       </c>
       <c r="G15">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L15">
         <v>4.673523904256721</v>
@@ -1472,10 +1472,10 @@
         <v>68</v>
       </c>
       <c r="P15">
-        <v>3.770163053558897</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q15">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R15">
         <v>4</v>
@@ -1484,10 +1484,10 @@
         <v>70</v>
       </c>
       <c r="T15">
-        <v>-0.03864807852496854</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U15">
-        <v>0.229836946441103</v>
+        <v>-0.2240926546957844</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1498,25 +1498,25 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>15.048</v>
+        <v>15.328</v>
       </c>
       <c r="D16">
-        <v>14.824</v>
+        <v>14.864</v>
       </c>
       <c r="E16">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="F16">
         <v>14.2</v>
       </c>
       <c r="G16">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="L16">
         <v>6.129350049043507</v>
@@ -1531,10 +1531,10 @@
         <v>68</v>
       </c>
       <c r="P16">
-        <v>14.85295632081913</v>
+        <v>14.78112560442925</v>
       </c>
       <c r="Q16">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R16">
         <v>15</v>
@@ -1543,10 +1543,10 @@
         <v>70</v>
       </c>
       <c r="T16">
-        <v>-0.152258195218657</v>
+        <v>-0.2718724935154491</v>
       </c>
       <c r="U16">
-        <v>0.1470436791808698</v>
+        <v>0.2188743955707473</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1557,25 +1557,25 @@
         <v>64</v>
       </c>
       <c r="C17">
-        <v>7.352</v>
+        <v>7.492</v>
       </c>
       <c r="D17">
-        <v>5.764</v>
+        <v>5.94</v>
       </c>
       <c r="E17">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="F17">
         <v>5.8</v>
       </c>
       <c r="G17">
-        <v>6.585563921872306</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="L17">
         <v>3.997862832988686</v>
@@ -1590,10 +1590,10 @@
         <v>68</v>
       </c>
       <c r="P17">
-        <v>4.753220574294097</v>
+        <v>5.11811531334273</v>
       </c>
       <c r="Q17">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R17">
         <v>5</v>
@@ -1602,10 +1602,10 @@
         <v>70</v>
       </c>
       <c r="T17">
-        <v>-0.04872543690873066</v>
+        <v>-0.09413862039851129</v>
       </c>
       <c r="U17">
-        <v>0.2467794257059026</v>
+        <v>-0.11811531334273</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1616,25 +1616,25 @@
         <v>64</v>
       </c>
       <c r="C18">
-        <v>172.1</v>
+        <v>171.868</v>
       </c>
       <c r="D18">
-        <v>175.156</v>
+        <v>174.552</v>
       </c>
       <c r="E18">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F18">
         <v>172.6</v>
       </c>
       <c r="G18">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L18">
         <v>24.70132137894479</v>
@@ -1649,22 +1649,22 @@
         <v>68</v>
       </c>
       <c r="P18">
-        <v>173.8081494148196</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q18">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R18">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S18" t="s">
         <v>70</v>
       </c>
       <c r="T18">
-        <v>-1.781713658384717</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U18">
-        <v>0.1918505851803616</v>
+        <v>-0.4018190334304563</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -1675,25 +1675,25 @@
         <v>64</v>
       </c>
       <c r="C19">
-        <v>5.304</v>
+        <v>5.384</v>
       </c>
       <c r="D19">
-        <v>4.316</v>
+        <v>4.436</v>
       </c>
       <c r="E19">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F19">
         <v>4.4</v>
       </c>
       <c r="G19">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
       </c>
       <c r="K19">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L19">
         <v>2.858585552684069</v>
@@ -1708,10 +1708,10 @@
         <v>68</v>
       </c>
       <c r="P19">
-        <v>3.994458620063688</v>
+        <v>4.212305297947762</v>
       </c>
       <c r="Q19">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -1720,10 +1720,10 @@
         <v>70</v>
       </c>
       <c r="T19">
-        <v>-0.04094734053139382</v>
+        <v>-0.07747785760363346</v>
       </c>
       <c r="U19">
-        <v>0.005541379936312207</v>
+        <v>-0.2123052979477622</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -1734,25 +1734,25 @@
         <v>65</v>
       </c>
       <c r="C20">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="D20">
-        <v>0.512</v>
+        <v>0.496</v>
       </c>
       <c r="E20">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="F20">
         <v>0.4</v>
       </c>
       <c r="G20">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
       </c>
       <c r="K20">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="L20">
         <v>0.8079772006265793</v>
@@ -1767,10 +1767,10 @@
         <v>68</v>
       </c>
       <c r="P20">
-        <v>0.689041649067501</v>
+        <v>0.6719736906377493</v>
       </c>
       <c r="Q20">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -1779,10 +1779,10 @@
         <v>70</v>
       </c>
       <c r="T20">
-        <v>-0.1112590907038641</v>
+        <v>-0.1148433417649544</v>
       </c>
       <c r="U20">
-        <v>0.310958350932499</v>
+        <v>0.3280263093622507</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -1793,19 +1793,19 @@
         <v>65</v>
       </c>
       <c r="C21">
-        <v>0.236</v>
+        <v>0.244</v>
       </c>
       <c r="D21">
-        <v>0.184</v>
+        <v>0.188</v>
       </c>
       <c r="E21">
-        <v>-0.05756181698960205</v>
+        <v>-0.06175632720386842</v>
       </c>
       <c r="F21">
         <v>0.2</v>
       </c>
       <c r="G21">
-        <v>0.2115586961462879</v>
+        <v>0.2176785958498485</v>
       </c>
       <c r="J21" t="s">
         <v>4</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>65</v>
       </c>
       <c r="C22">
-        <v>1.164</v>
+        <v>1.168</v>
       </c>
       <c r="D22">
-        <v>1.34</v>
+        <v>1.328</v>
       </c>
       <c r="E22">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="F22">
         <v>1.4</v>
       </c>
       <c r="G22">
-        <v>1.246724413043333</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="J22" t="s">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="L22">
         <v>0.9319718387197466</v>
@@ -1885,10 +1885,10 @@
         <v>68</v>
       </c>
       <c r="P22">
-        <v>1.06279383028951</v>
+        <v>0.9726626509918868</v>
       </c>
       <c r="Q22">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -1897,10 +1897,10 @@
         <v>70</v>
       </c>
       <c r="T22">
-        <v>-0.1716086035201392</v>
+        <v>-0.1662324445230186</v>
       </c>
       <c r="U22">
-        <v>-0.06279383028951013</v>
+        <v>0.02733734900811324</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -1911,25 +1911,25 @@
         <v>65</v>
       </c>
       <c r="C23">
-        <v>0.612</v>
+        <v>0.6</v>
       </c>
       <c r="D23">
-        <v>0.732</v>
+        <v>0.696</v>
       </c>
       <c r="E23">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F23">
         <v>0.6</v>
       </c>
       <c r="G23">
-        <v>0.6684030088931816</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J23" t="s">
         <v>4</v>
       </c>
       <c r="K23">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L23">
         <v>1.559831022862906</v>
@@ -1944,10 +1944,10 @@
         <v>68</v>
       </c>
       <c r="P23">
-        <v>0.2835868085528425</v>
+        <v>0.2767323416308665</v>
       </c>
       <c r="Q23">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -1956,10 +1956,10 @@
         <v>70</v>
       </c>
       <c r="T23">
-        <v>-0.04579057085721838</v>
+        <v>-0.04729480830888999</v>
       </c>
       <c r="U23">
-        <v>-0.2835868085528425</v>
+        <v>-0.2767323416308665</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -1970,25 +1970,25 @@
         <v>65</v>
       </c>
       <c r="C24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="D24">
-        <v>1.54</v>
+        <v>1.584</v>
       </c>
       <c r="E24">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="F24">
         <v>1.6</v>
       </c>
       <c r="G24">
-        <v>1.730790973320455</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="L24">
         <v>1.157976831184469</v>
@@ -2003,10 +2003,10 @@
         <v>68</v>
       </c>
       <c r="P24">
-        <v>1.231964530182992</v>
+        <v>1.299486100486649</v>
       </c>
       <c r="Q24">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2015,10 +2015,10 @@
         <v>70</v>
       </c>
       <c r="T24">
-        <v>-0.1989244824214469</v>
+        <v>-0.2220880496308713</v>
       </c>
       <c r="U24">
-        <v>-0.2319645301829925</v>
+        <v>-0.2994861004866491</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -2029,19 +2029,19 @@
         <v>65</v>
       </c>
       <c r="C25">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D25">
-        <v>0.612</v>
+        <v>0.608</v>
       </c>
       <c r="E25">
-        <v>-0.005331174175850051</v>
+        <v>-0.01550360442781762</v>
       </c>
       <c r="F25">
         <v>0.6</v>
       </c>
       <c r="G25">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="J25" t="s">
         <v>4</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2088,25 +2088,25 @@
         <v>65</v>
       </c>
       <c r="C26">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D26">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E26">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F26">
         <v>12.4</v>
       </c>
       <c r="G26">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J26" t="s">
         <v>4</v>
       </c>
       <c r="K26">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L26">
         <v>2.351026032651849</v>
@@ -2121,10 +2121,10 @@
         <v>68</v>
       </c>
       <c r="P26">
-        <v>9.674452691001546</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q26">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2133,10 +2133,10 @@
         <v>70</v>
       </c>
       <c r="T26">
-        <v>-1.562127356038731</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U26">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -2147,25 +2147,25 @@
         <v>65</v>
       </c>
       <c r="C27">
-        <v>1.736</v>
+        <v>1.604</v>
       </c>
       <c r="D27">
-        <v>1.98</v>
+        <v>1.924</v>
       </c>
       <c r="E27">
-        <v>0.06755162617559574</v>
+        <v>-0.1313628720128142</v>
       </c>
       <c r="F27">
         <v>2.4</v>
       </c>
       <c r="G27">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>1.736334852416627</v>
@@ -2180,10 +2180,10 @@
         <v>68</v>
       </c>
       <c r="P27">
-        <v>0.05816049090560802</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2192,10 +2192,10 @@
         <v>70</v>
       </c>
       <c r="T27">
-        <v>-0.009391135269987715</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>-0.05816049090560802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -2206,25 +2206,25 @@
         <v>65</v>
       </c>
       <c r="C28">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
       <c r="D28">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="E28">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F28">
         <v>0.2</v>
       </c>
       <c r="G28">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J28" t="s">
         <v>4</v>
       </c>
       <c r="K28">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L28">
         <v>0.4925498319332764</v>
@@ -2239,10 +2239,10 @@
         <v>68</v>
       </c>
       <c r="P28">
-        <v>0.7880676051329962</v>
+        <v>0.7802977676584159</v>
       </c>
       <c r="Q28">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -2251,10 +2251,10 @@
         <v>70</v>
       </c>
       <c r="T28">
-        <v>0.09755932516498467</v>
+        <v>0.101489785235631</v>
       </c>
       <c r="U28">
-        <v>0.2119323948670038</v>
+        <v>0.2197022323415841</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -2268,22 +2268,22 @@
         <v>0.632</v>
       </c>
       <c r="D29">
-        <v>0.416</v>
+        <v>0.44</v>
       </c>
       <c r="E29">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F29">
         <v>0.4</v>
       </c>
       <c r="G29">
-        <v>0.530474583992273</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J29" t="s">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L29">
         <v>0.7620693762924241</v>
@@ -2298,10 +2298,10 @@
         <v>68</v>
       </c>
       <c r="P29">
-        <v>0.7484613503089816</v>
+        <v>0.8656925512363728</v>
       </c>
       <c r="Q29">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -2310,10 +2310,10 @@
         <v>70</v>
       </c>
       <c r="T29">
-        <v>0.0926562439219849</v>
+        <v>0.1125966967311974</v>
       </c>
       <c r="U29">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -2357,10 +2357,10 @@
         <v>68</v>
       </c>
       <c r="P30">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="Q30">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -2369,10 +2369,10 @@
         <v>70</v>
       </c>
       <c r="T30">
-        <v>0.141286249557361</v>
+        <v>0.1495117733786751</v>
       </c>
       <c r="U30">
-        <v>-0.141286249557361</v>
+        <v>-0.1495117733786751</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -2383,25 +2383,25 @@
         <v>65</v>
       </c>
       <c r="C31">
-        <v>0.716</v>
+        <v>0.74</v>
       </c>
       <c r="D31">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="E31">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="F31">
         <v>0.6</v>
       </c>
       <c r="G31">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="L31">
         <v>0.3332002265469857</v>
@@ -2416,10 +2416,10 @@
         <v>68</v>
       </c>
       <c r="P31">
-        <v>1.096603770057717</v>
+        <v>1.14215441807513</v>
       </c>
       <c r="Q31">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -2428,10 +2428,10 @@
         <v>70</v>
       </c>
       <c r="T31">
-        <v>0.135754753885809</v>
+        <v>0.1485548356036258</v>
       </c>
       <c r="U31">
-        <v>-0.09660377005771714</v>
+        <v>-0.1421544180751302</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -2442,25 +2442,25 @@
         <v>65</v>
       </c>
       <c r="C32">
-        <v>1.084</v>
+        <v>1.12</v>
       </c>
       <c r="D32">
-        <v>1.172</v>
+        <v>1.168</v>
       </c>
       <c r="E32">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="J32" t="s">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="L32">
         <v>0.8500971208676269</v>
@@ -2475,10 +2475,10 @@
         <v>68</v>
       </c>
       <c r="P32">
-        <v>2.00997599986936</v>
+        <v>2.046609860316908</v>
       </c>
       <c r="Q32">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R32">
         <v>2</v>
@@ -2487,10 +2487,10 @@
         <v>70</v>
       </c>
       <c r="T32">
-        <v>0.2488262439260871</v>
+        <v>0.2661932454427003</v>
       </c>
       <c r="U32">
-        <v>-0.009975999869360042</v>
+        <v>-0.04660986031690806</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -2501,25 +2501,25 @@
         <v>65</v>
       </c>
       <c r="C33">
-        <v>0.552</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D33">
-        <v>0.392</v>
+        <v>0.408</v>
       </c>
       <c r="E33">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F33">
         <v>0.4</v>
       </c>
       <c r="G33">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J33" t="s">
         <v>4</v>
       </c>
       <c r="K33">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L33">
         <v>0.3921195507989373</v>
@@ -2534,10 +2534,10 @@
         <v>68</v>
       </c>
       <c r="P33">
-        <v>0.3085361649247209</v>
+        <v>0.3618566504167141</v>
       </c>
       <c r="Q33">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -2546,10 +2546,10 @@
         <v>70</v>
       </c>
       <c r="T33">
-        <v>0.03819542872082443</v>
+        <v>0.04706505036799469</v>
       </c>
       <c r="U33">
-        <v>-0.3085361649247209</v>
+        <v>-0.3618566504167141</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -2560,25 +2560,25 @@
         <v>65</v>
       </c>
       <c r="C34">
-        <v>10.028</v>
+        <v>9.932</v>
       </c>
       <c r="D34">
-        <v>11.468</v>
+        <v>11.352</v>
       </c>
       <c r="E34">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F34">
         <v>11.6</v>
       </c>
       <c r="G34">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J34" t="s">
         <v>4</v>
       </c>
       <c r="K34">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L34">
         <v>3.050242274051084</v>
@@ -2593,10 +2593,10 @@
         <v>68</v>
       </c>
       <c r="P34">
-        <v>15.15860750983988</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q34">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R34">
         <v>15</v>
@@ -2605,10 +2605,10 @@
         <v>70</v>
       </c>
       <c r="T34">
-        <v>1.876569357081072</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U34">
-        <v>-0.158607509839884</v>
+        <v>0.2118155723185868</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -2622,22 +2622,22 @@
         <v>0.632</v>
       </c>
       <c r="D35">
-        <v>0.416</v>
+        <v>0.44</v>
       </c>
       <c r="E35">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F35">
         <v>0.4</v>
       </c>
       <c r="G35">
-        <v>0.530474583992273</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J35" t="s">
         <v>4</v>
       </c>
       <c r="K35">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L35">
         <v>0.7620693762924241</v>
@@ -2652,10 +2652,10 @@
         <v>68</v>
       </c>
       <c r="P35">
-        <v>0.7484613503089816</v>
+        <v>0.8656925512363728</v>
       </c>
       <c r="Q35">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -2664,10 +2664,10 @@
         <v>70</v>
       </c>
       <c r="T35">
-        <v>0.0926562439219849</v>
+        <v>0.1125966967311974</v>
       </c>
       <c r="U35">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -2724,7 +2724,7 @@
         <v>67</v>
       </c>
       <c r="R38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S38" t="s">
         <v>70</v>
@@ -2744,7 +2744,7 @@
         <v>67</v>
       </c>
       <c r="R39">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S39" t="s">
         <v>70</v>
@@ -2804,7 +2804,7 @@
         <v>67</v>
       </c>
       <c r="R42">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S42" t="s">
         <v>70</v>
@@ -2824,7 +2824,7 @@
         <v>67</v>
       </c>
       <c r="R43">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="S43" t="s">
         <v>70</v>

--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -573,28 +573,28 @@
         <v>0.5141399999999998</v>
       </c>
       <c r="D2">
-        <v>0.4962479999999996</v>
+        <v>0.4961759999999997</v>
       </c>
       <c r="E2">
-        <v>0.496420004125868</v>
+        <v>0.4965980195557412</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064233115088753</v>
+        <v>0.5063922584364764</v>
       </c>
       <c r="H2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="I2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -609,7 +609,7 @@
         <v>35</v>
       </c>
       <c r="R2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="S2" t="s">
         <v>36</v>
@@ -629,28 +629,28 @@
         <v>0.4579319999999985</v>
       </c>
       <c r="D3">
-        <v>0.4751159999999989</v>
+        <v>0.4751759999999988</v>
       </c>
       <c r="E3">
-        <v>0.4730562578730623</v>
+        <v>0.4728409805834767</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4653433332792005</v>
+        <v>0.4653692108395329</v>
       </c>
       <c r="H3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="I3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -665,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="R3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>

--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -570,31 +570,31 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>0.5141399999999998</v>
+        <v>0.5143399999999999</v>
       </c>
       <c r="D2">
-        <v>0.4961759999999997</v>
+        <v>0.4959839999999996</v>
       </c>
       <c r="E2">
-        <v>0.4965980195557412</v>
+        <v>0.4965387457485618</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5063922584364764</v>
+        <v>0.5064231917089714</v>
       </c>
       <c r="H2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="I2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -609,7 +609,7 @@
         <v>35</v>
       </c>
       <c r="R2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="S2" t="s">
         <v>36</v>
@@ -626,31 +626,31 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.4579319999999985</v>
+        <v>0.4577039999999986</v>
       </c>
       <c r="D3">
-        <v>0.4751759999999988</v>
+        <v>0.4752959999999988</v>
       </c>
       <c r="E3">
-        <v>0.4728409805834767</v>
+        <v>0.4728389431404009</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4653692108395329</v>
+        <v>0.4652913006894609</v>
       </c>
       <c r="H3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="I3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -665,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="R3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>

--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -570,7 +570,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>0.5143399999999999</v>
+        <v>0.51434</v>
       </c>
       <c r="D2">
         <v>0.4959839999999996</v>
@@ -582,7 +582,7 @@
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064231917089714</v>
+        <v>0.5064231917089715</v>
       </c>
       <c r="H2">
         <v>0.5264302802913263</v>
@@ -626,7 +626,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.4577039999999986</v>
+        <v>0.4577039999999984</v>
       </c>
       <c r="D3">
         <v>0.4752959999999988</v>

--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -570,31 +570,31 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>0.51434</v>
+        <v>0.5142079999999999</v>
       </c>
       <c r="D2">
-        <v>0.4959839999999996</v>
+        <v>0.4958199999999996</v>
       </c>
       <c r="E2">
-        <v>0.4965387457485618</v>
+        <v>0.4976068069845513</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064231917089715</v>
+        <v>0.5062773903434608</v>
       </c>
       <c r="H2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="I2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -609,7 +609,7 @@
         <v>35</v>
       </c>
       <c r="R2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="S2" t="s">
         <v>36</v>
@@ -626,31 +626,31 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.4577039999999984</v>
+        <v>0.4576439999999986</v>
       </c>
       <c r="D3">
-        <v>0.4752959999999988</v>
+        <v>0.4753639999999988</v>
       </c>
       <c r="E3">
-        <v>0.4728389431404009</v>
+        <v>0.4714935259345234</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4652913006894609</v>
+        <v>0.4652865061515034</v>
       </c>
       <c r="H3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="I3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -665,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="R3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>

--- a/outputs/Block3_Constrained_Predictions.xlsx
+++ b/outputs/Block3_Constrained_Predictions.xlsx
@@ -570,31 +570,31 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>0.5142079999999999</v>
+        <v>0.5143840000000001</v>
       </c>
       <c r="D2">
-        <v>0.4958199999999996</v>
+        <v>0.4959679999999996</v>
       </c>
       <c r="E2">
-        <v>0.4976068069845513</v>
+        <v>0.4972024416993439</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5062773903434608</v>
+        <v>0.506441314148639</v>
       </c>
       <c r="H2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="I2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -609,7 +609,7 @@
         <v>35</v>
       </c>
       <c r="R2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="S2" t="s">
         <v>36</v>
@@ -626,31 +626,31 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.4576439999999986</v>
+        <v>0.4577239999999985</v>
       </c>
       <c r="D3">
-        <v>0.4753639999999988</v>
+        <v>0.4752239999999988</v>
       </c>
       <c r="E3">
-        <v>0.4714935259345234</v>
+        <v>0.471947408691133</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4652865061515034</v>
+        <v>0.4652716217636178</v>
       </c>
       <c r="H3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="I3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -665,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="R3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>
